--- a/assets/docs/relatorios/gestao-para-resultados-2026-05/turma 1/participantes.xlsx
+++ b/assets/docs/relatorios/gestao-para-resultados-2026-05/turma 1/participantes.xlsx
@@ -35,12 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1035,7 +1031,7 @@
         <v>Ingresso Único</v>
       </c>
       <c r="G22" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H22" t="str">
         <v>2026-05-22 12:33:16</v>
